--- a/Convert_from_xlsx_to_Json/table_normalization/food-table12.xlsx
+++ b/Convert_from_xlsx_to_Json/table_normalization/food-table12.xlsx
@@ -210,7 +210,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
@@ -249,34 +249,37 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -667,10 +670,10 @@
       <c r="K3" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="L3" s="19" t="s">
+      <c r="L3" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="M3" s="29" t="s">
+      <c r="M3" s="30" t="s">
         <v>8</v>
       </c>
       <c r="N3" s="14"/>
